--- a/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 28,4</t>
+          <t>20,77; 28,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,31; 38,0</t>
+          <t>28,99; 38,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,51; 37,6</t>
+          <t>28,29; 37,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,32; 37,5</t>
+          <t>21,02; 37,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,36; 44,25</t>
+          <t>34,59; 43,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,57; 49,13</t>
+          <t>39,34; 49,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,4; 41,26</t>
+          <t>32,15; 41,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,51; 35,67</t>
+          <t>21,38; 35,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,61; 34,95</t>
+          <t>28,85; 34,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,47; 41,91</t>
+          <t>35,33; 41,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 37,88</t>
+          <t>31,31; 37,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,31; 34,78</t>
+          <t>23,15; 34,3</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,43; 34,32</t>
+          <t>27,3; 34,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 44,15</t>
+          <t>36,91; 44,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,74; 34,64</t>
+          <t>26,25; 34,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,87; 34,9</t>
+          <t>23,43; 34,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,96; 48,67</t>
+          <t>40,24; 49,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,08; 53,86</t>
+          <t>45,47; 53,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,66; 45,98</t>
+          <t>38,03; 46,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 29,88</t>
+          <t>15,52; 30,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,61; 39,77</t>
+          <t>34,83; 40,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,01; 47,75</t>
+          <t>42,16; 47,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,93; 38,68</t>
+          <t>32,92; 38,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 30,3</t>
+          <t>20,09; 30,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,11; 40,73</t>
+          <t>32,88; 40,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,66; 46,46</t>
+          <t>38,96; 46,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,91; 40,29</t>
+          <t>33,03; 40,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,83; 28,86</t>
+          <t>21,73; 29,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,06; 59,46</t>
+          <t>52,15; 59,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,39; 62,1</t>
+          <t>54,34; 62,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,48; 53,92</t>
+          <t>46,62; 54,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,33; 33,43</t>
+          <t>21,95; 33,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,95; 49,24</t>
+          <t>43,88; 49,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,7; 53,44</t>
+          <t>47,9; 53,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,41; 46,21</t>
+          <t>40,48; 46,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,09; 29,96</t>
+          <t>23,2; 30,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,28; 55,77</t>
+          <t>46,32; 55,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,71; 56,24</t>
+          <t>47,51; 56,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,3; 59,53</t>
+          <t>50,8; 59,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 40,12</t>
+          <t>12,21; 39,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,71; 71,02</t>
+          <t>62,44; 70,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,83; 76,99</t>
+          <t>69,42; 77,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,09; 65,85</t>
+          <t>57,94; 65,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,33; 45,29</t>
+          <t>34,75; 45,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,72; 61,96</t>
+          <t>55,47; 61,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,49; 65,72</t>
+          <t>59,96; 65,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55,93; 61,46</t>
+          <t>55,65; 61,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 41,13</t>
+          <t>21,79; 41,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,47; 80,72</t>
+          <t>72,6; 81,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,34; 81,51</t>
+          <t>73,21; 81,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,32; 71,6</t>
+          <t>61,97; 71,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49,12; 56,94</t>
+          <t>48,86; 56,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,03; 83,94</t>
+          <t>76,39; 83,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,45; 90,91</t>
+          <t>84,25; 90,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,8; 86,59</t>
+          <t>79,02; 86,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,61; 57,95</t>
+          <t>51,73; 58,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75,35; 81,25</t>
+          <t>75,54; 81,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80,05; 85,5</t>
+          <t>80,11; 85,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,91</t>
+          <t>72,08; 78,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,31; 56,32</t>
+          <t>51,43; 56,4</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,23; 85,46</t>
+          <t>76,17; 85,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,91; 96,5</t>
+          <t>90,53; 96,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,25; 92,33</t>
+          <t>84,87; 91,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,06; 58,16</t>
+          <t>50,5; 58,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,62; 95,18</t>
+          <t>89,94; 95,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91,41; 96,56</t>
+          <t>91,37; 96,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,92; 94,27</t>
+          <t>87,98; 93,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,36; 90,15</t>
+          <t>64,55; 89,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84,65; 89,78</t>
+          <t>84,56; 89,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92,26; 96,06</t>
+          <t>91,88; 95,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87,58; 92,25</t>
+          <t>87,64; 92,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59,48; 82,78</t>
+          <t>59,35; 83,49</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,93; 95,95</t>
+          <t>88,71; 96,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92,03; 97,47</t>
+          <t>91,57; 97,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,96; 96,09</t>
+          <t>90,37; 96,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,89; 76,27</t>
+          <t>67,69; 76,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,96; 97,84</t>
+          <t>92,98; 97,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,33; 98,82</t>
+          <t>95,28; 98,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,54; 98,43</t>
+          <t>94,41; 98,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,48; 79,76</t>
+          <t>73,38; 79,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>92,6; 96,52</t>
+          <t>92,31; 96,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,8; 97,79</t>
+          <t>94,67; 97,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93,72; 96,94</t>
+          <t>93,63; 96,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,25; 77,46</t>
+          <t>72,22; 76,95</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,39; 50,01</t>
+          <t>46,41; 49,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>53,97; 57,43</t>
+          <t>53,99; 57,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50,46; 54,0</t>
+          <t>50,52; 53,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,22; 41,85</t>
+          <t>29,55; 41,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,17; 65,77</t>
+          <t>62,3; 65,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,55; 70,8</t>
+          <t>67,7; 70,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,12; 65,31</t>
+          <t>62,21; 65,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,17; 58,07</t>
+          <t>44,01; 58,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,87; 57,41</t>
+          <t>54,92; 57,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61,35; 63,74</t>
+          <t>61,46; 63,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56,91; 59,33</t>
+          <t>57,0; 59,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,27; 48,31</t>
+          <t>39,36; 47,74</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>102838; 140306</t>
+          <t>102636; 139762</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>133108; 172570</t>
+          <t>131676; 173771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115383; 157707</t>
+          <t>118665; 159125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85274; 149996</t>
+          <t>84062; 149159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>165311; 206844</t>
+          <t>161724; 203204</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>170228; 211365</t>
+          <t>169248; 211115</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>128237; 163304</t>
+          <t>127239; 164726</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67357; 111716</t>
+          <t>66973; 111138</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>275099; 336043</t>
+          <t>277386; 332048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313648; 370648</t>
+          <t>312413; 371133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>253359; 308772</t>
+          <t>255241; 309145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>166270; 248037</t>
+          <t>165126; 244639</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>201778; 252417</t>
+          <t>200812; 252799</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>251483; 303318</t>
+          <t>253601; 307473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>157914; 204548</t>
+          <t>155028; 201115</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96882; 147829</t>
+          <t>99239; 146118</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>256185; 304457</t>
+          <t>251684; 307976</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>275132; 328657</t>
+          <t>277479; 328487</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>212259; 259110</t>
+          <t>214339; 261046</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77256; 153002</t>
+          <t>79495; 155836</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>471098; 541283</t>
+          <t>474040; 544982</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>545053; 619537</t>
+          <t>547024; 619394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>379991; 446376</t>
+          <t>379943; 445076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>184399; 283529</t>
+          <t>188016; 284718</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>211434; 260125</t>
+          <t>210000; 261131</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>263591; 316814</t>
+          <t>265647; 319188</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>220189; 269596</t>
+          <t>220995; 270743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111711; 154776</t>
+          <t>116543; 157272</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>359075; 410099</t>
+          <t>359726; 410045</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>386596; 441451</t>
+          <t>386292; 443218</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>307410; 356601</t>
+          <t>308319; 358037</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>138085; 197884</t>
+          <t>129923; 199968</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>583804; 654105</t>
+          <t>582841; 658408</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>664363; 744334</t>
+          <t>667174; 744638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>537636; 614826</t>
+          <t>538570; 613279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>260517; 338033</t>
+          <t>261730; 338470</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>240270; 289506</t>
+          <t>240465; 288703</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>293245; 345630</t>
+          <t>291982; 344542</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>331420; 384619</t>
+          <t>328173; 382048</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109359; 356138</t>
+          <t>108373; 354972</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>323353; 366199</t>
+          <t>321970; 363940</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>430275; 474393</t>
+          <t>427790; 475250</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>377078; 427388</t>
+          <t>376058; 427592</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>251874; 322842</t>
+          <t>247699; 322565</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>576605; 641161</t>
+          <t>573985; 638035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>732252; 808926</t>
+          <t>737953; 809741</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>724322; 795924</t>
+          <t>720727; 792782</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>309109; 658388</t>
+          <t>348805; 662693</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>280242; 312156</t>
+          <t>280760; 313730</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>314930; 350034</t>
+          <t>314390; 349609</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>297855; 342210</t>
+          <t>296152; 341565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>275695; 319587</t>
+          <t>274241; 319166</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>307149; 339117</t>
+          <t>308586; 338998</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>378147; 407101</t>
+          <t>377263; 405913</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>391522; 430215</t>
+          <t>392598; 428656</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>282777; 317537</t>
+          <t>283458; 319988</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>595805; 642477</t>
+          <t>597277; 642371</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>702264; 749988</t>
+          <t>702776; 749406</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>701916; 759400</t>
+          <t>702578; 761040</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>569116; 624616</t>
+          <t>570430; 625548</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>223041; 250035</t>
+          <t>222856; 249038</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>281630; 298939</t>
+          <t>280453; 298815</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>285028; 308694</t>
+          <t>283739; 307424</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184305; 214125</t>
+          <t>185915; 216279</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>307329; 326417</t>
+          <t>308432; 326890</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>323591; 341810</t>
+          <t>323440; 342125</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>332137; 356119</t>
+          <t>332340; 354968</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>391568; 548461</t>
+          <t>392704; 545258</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>537937; 570572</t>
+          <t>537411; 569981</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>612387; 637608</t>
+          <t>609912; 636922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>623634; 656923</t>
+          <t>624066; 657327</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>580850; 808391</t>
+          <t>579561; 815314</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>186644; 201387</t>
+          <t>186186; 201800</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>229931; 243521</t>
+          <t>228793; 243440</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231208; 246955</t>
+          <t>232261; 246847</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>191958; 215657</t>
+          <t>191394; 214947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>310404; 326708</t>
+          <t>310479; 326332</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>370801; 384390</t>
+          <t>370611; 384354</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>378317; 393901</t>
+          <t>377794; 393809</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>312901; 339641</t>
+          <t>312495; 337242</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>503545; 524851</t>
+          <t>501991; 524118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>605604; 624702</t>
+          <t>604784; 624461</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>615909; 637079</t>
+          <t>615331; 637126</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>511923; 548887</t>
+          <t>511715; 545290</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1519872; 1638673</t>
+          <t>1520616; 1636835</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1849476; 1968067</t>
+          <t>1850019; 1965044</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1712701; 1832928</t>
+          <t>1714718; 1829476</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1045718; 1448031</t>
+          <t>1022275; 1443659</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2100896; 2222608</t>
+          <t>2105314; 2214989</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2403543; 2519341</t>
+          <t>2409124; 2519358</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2202021; 2314803</t>
+          <t>2204921; 2318325</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1639887; 2155738</t>
+          <t>1633608; 2158123</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652324; 3821214</t>
+          <t>3655098; 3821684</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4285196; 4452118</t>
+          <t>4292739; 4457638</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3949120; 4116959</t>
+          <t>3954961; 4114052</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2816485; 3464703</t>
+          <t>2822782; 3424282</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,77; 28,29</t>
+          <t>20,97; 28,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,99; 38,26</t>
+          <t>29,2; 37,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,29; 37,94</t>
+          <t>27,78; 37,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,02; 37,29</t>
+          <t>17,41; 30,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,59; 43,47</t>
+          <t>34,75; 43,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,34; 49,07</t>
+          <t>39,23; 48,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,15; 41,62</t>
+          <t>32,22; 41,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,38; 35,48</t>
+          <t>21,75; 34,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,85; 34,53</t>
+          <t>29,06; 34,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,33; 41,97</t>
+          <t>35,33; 41,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,31; 37,92</t>
+          <t>31,26; 38,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,15; 34,3</t>
+          <t>21,62; 31,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,3; 34,37</t>
+          <t>27,98; 34,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,91; 44,75</t>
+          <t>36,85; 44,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,25; 34,06</t>
+          <t>26,73; 34,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,43; 34,5</t>
+          <t>22,16; 32,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,24; 49,24</t>
+          <t>40,49; 48,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,47; 53,83</t>
+          <t>45,36; 53,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,03; 46,32</t>
+          <t>37,96; 45,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,52; 30,43</t>
+          <t>22,55; 30,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,83; 40,04</t>
+          <t>35,0; 40,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,16; 47,74</t>
+          <t>41,81; 47,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,92; 38,57</t>
+          <t>33,38; 38,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,09; 30,43</t>
+          <t>23,48; 30,2</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,88; 40,89</t>
+          <t>32,84; 41,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,96; 46,81</t>
+          <t>39,04; 46,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,03; 40,46</t>
+          <t>32,73; 40,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,73; 29,32</t>
+          <t>20,61; 27,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,15; 59,45</t>
+          <t>52,25; 59,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,34; 62,35</t>
+          <t>54,31; 61,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,62; 54,13</t>
+          <t>46,53; 53,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,95; 33,78</t>
+          <t>28,52; 34,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,88; 49,56</t>
+          <t>43,71; 49,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,9; 53,47</t>
+          <t>47,98; 53,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,48; 46,09</t>
+          <t>40,68; 46,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,2; 30,0</t>
+          <t>25,55; 30,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,32; 55,61</t>
+          <t>46,33; 55,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,51; 56,06</t>
+          <t>47,67; 56,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,8; 59,14</t>
+          <t>50,81; 58,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 39,98</t>
+          <t>34,56; 42,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,44; 70,58</t>
+          <t>62,87; 70,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,42; 77,13</t>
+          <t>69,51; 77,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,94; 65,88</t>
+          <t>57,76; 65,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,75; 45,25</t>
+          <t>40,2; 45,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,47; 61,66</t>
+          <t>55,5; 61,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,96; 65,79</t>
+          <t>59,88; 65,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55,65; 61,21</t>
+          <t>55,74; 61,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,79; 41,4</t>
+          <t>38,49; 43,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,6; 81,13</t>
+          <t>72,52; 80,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,21; 81,41</t>
+          <t>73,31; 81,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,97; 71,47</t>
+          <t>62,47; 71,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,86; 56,87</t>
+          <t>47,48; 55,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,39; 83,91</t>
+          <t>76,12; 83,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,25; 90,65</t>
+          <t>84,29; 90,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,02; 86,27</t>
+          <t>78,55; 86,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,73; 58,4</t>
+          <t>52,22; 58,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75,54; 81,24</t>
+          <t>75,25; 81,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80,11; 85,43</t>
+          <t>79,69; 85,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,08; 78,07</t>
+          <t>71,96; 77,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,43; 56,4</t>
+          <t>51,07; 55,97</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,17; 85,12</t>
+          <t>75,85; 85,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,53; 96,46</t>
+          <t>90,77; 96,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,87; 91,95</t>
+          <t>84,85; 91,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,5; 58,75</t>
+          <t>49,54; 57,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,94; 95,32</t>
+          <t>89,84; 95,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91,37; 96,65</t>
+          <t>91,78; 96,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,98; 93,97</t>
+          <t>88,02; 94,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64,55; 89,63</t>
+          <t>62,38; 68,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84,56; 89,69</t>
+          <t>84,65; 89,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91,88; 95,95</t>
+          <t>92,33; 96,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87,64; 92,31</t>
+          <t>87,57; 92,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59,35; 83,49</t>
+          <t>57,13; 62,74</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,71; 96,15</t>
+          <t>88,59; 95,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91,57; 97,43</t>
+          <t>92,06; 97,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,37; 96,05</t>
+          <t>90,61; 95,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,69; 76,02</t>
+          <t>67,29; 76,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,98; 97,73</t>
+          <t>92,93; 97,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,28; 98,81</t>
+          <t>95,04; 98,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,41; 98,41</t>
+          <t>93,94; 98,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,38; 79,2</t>
+          <t>73,18; 78,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>92,31; 96,38</t>
+          <t>92,41; 96,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,67; 97,75</t>
+          <t>94,65; 97,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93,63; 96,95</t>
+          <t>93,71; 96,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,22; 76,95</t>
+          <t>71,97; 76,74</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,41; 49,96</t>
+          <t>46,5; 50,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>53,99; 57,34</t>
+          <t>53,81; 57,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50,52; 53,9</t>
+          <t>50,34; 53,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,55; 41,73</t>
+          <t>37,91; 41,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>62,3; 65,55</t>
+          <t>62,11; 65,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,7; 70,8</t>
+          <t>67,48; 70,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,41</t>
+          <t>62,08; 65,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,01; 58,13</t>
+          <t>44,93; 47,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,92; 57,42</t>
+          <t>54,84; 57,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61,46; 63,82</t>
+          <t>61,34; 63,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57,0; 59,29</t>
+          <t>56,89; 59,25</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,36; 47,74</t>
+          <t>41,85; 44,24</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114838</t>
+          <t>96843</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>102244</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>202808</t>
+          <t>199087</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>102636; 139762</t>
+          <t>103589; 140569</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131676; 173771</t>
+          <t>132627; 171806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118665; 159125</t>
+          <t>116517; 158268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84062; 149159</t>
+          <t>70982; 124844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>161724; 203204</t>
+          <t>162466; 205475</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>169248; 211115</t>
+          <t>168791; 208953</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>127239; 164726</t>
+          <t>127509; 163832</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66973; 111138</t>
+          <t>78855; 126144</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>277386; 332048</t>
+          <t>279461; 331610</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>312413; 371133</t>
+          <t>312441; 369049</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>255241; 309145</t>
+          <t>254837; 310636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>165126; 244639</t>
+          <t>166553; 239491</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121227</t>
+          <t>128500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>133062</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>245558</t>
+          <t>261562</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>200812; 252799</t>
+          <t>205763; 254083</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>253601; 307473</t>
+          <t>253201; 305639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155028; 201115</t>
+          <t>157868; 201504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99239; 146118</t>
+          <t>105699; 155263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>251684; 307976</t>
+          <t>253257; 305722</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>277479; 328487</t>
+          <t>276804; 327419</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>214339; 261046</t>
+          <t>213927; 258707</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>79495; 155836</t>
+          <t>113125; 155381</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>474040; 544982</t>
+          <t>476312; 545253</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>547024; 619394</t>
+          <t>542411; 614436</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>379943; 445076</t>
+          <t>385223; 447573</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>188016; 284718</t>
+          <t>229753; 295511</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133721</t>
+          <t>150445</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>173986</t>
+          <t>197136</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>307707</t>
+          <t>347581</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>210000; 261131</t>
+          <t>209708; 262126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>265647; 319188</t>
+          <t>266181; 319372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>220995; 270743</t>
+          <t>218969; 273375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116543; 157272</t>
+          <t>127945; 172977</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>359726; 410045</t>
+          <t>360406; 412263</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>386292; 443218</t>
+          <t>386034; 439498</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>308319; 358037</t>
+          <t>307756; 356988</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>129923; 199968</t>
+          <t>177719; 216575</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>582841; 658408</t>
+          <t>580708; 660939</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>667174; 744638</t>
+          <t>668172; 744453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>538570; 613279</t>
+          <t>541306; 613733</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>261730; 338470</t>
+          <t>317837; 376627</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248815</t>
+          <t>268258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>296830</t>
+          <t>318176</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>545645</t>
+          <t>586435</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>240465; 288703</t>
+          <t>240544; 287527</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>291982; 344542</t>
+          <t>293009; 344612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>328173; 382048</t>
+          <t>328265; 380984</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108373; 354972</t>
+          <t>242120; 297481</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>321970; 363940</t>
+          <t>324172; 365643</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>427790; 475250</t>
+          <t>428341; 474815</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>376058; 427592</t>
+          <t>374933; 424929</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>247699; 322565</t>
+          <t>296197; 338169</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>573985; 638035</t>
+          <t>574270; 640427</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>737953; 809741</t>
+          <t>736953; 807201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>720727; 792782</t>
+          <t>721937; 793037</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>348805; 662693</t>
+          <t>553264; 619590</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>296422</t>
+          <t>313355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>301097</t>
+          <t>336355</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>597519</t>
+          <t>649711</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>280760; 313730</t>
+          <t>280448; 312809</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>314390; 349609</t>
+          <t>314828; 349484</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>296152; 341565</t>
+          <t>298546; 339853</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>274241; 319166</t>
+          <t>289346; 338486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>308586; 338998</t>
+          <t>307507; 338617</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>377263; 405913</t>
+          <t>377467; 406456</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>392598; 428656</t>
+          <t>390278; 428819</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>283458; 319988</t>
+          <t>317972; 355535</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>597277; 642371</t>
+          <t>595018; 642705</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>702776; 749406</t>
+          <t>699058; 746556</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>702578; 761040</t>
+          <t>701422; 756727</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>570430; 625548</t>
+          <t>622103; 681852</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200003</t>
+          <t>218401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>469225</t>
+          <t>288804</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>669228</t>
+          <t>507205</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>222856; 249038</t>
+          <t>221924; 249199</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>280453; 298815</t>
+          <t>281198; 298813</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>283739; 307424</t>
+          <t>283694; 306888</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>185915; 216279</t>
+          <t>201679; 235158</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>308432; 326890</t>
+          <t>308106; 326410</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>323440; 342125</t>
+          <t>324898; 342871</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>332340; 354968</t>
+          <t>332515; 355139</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>392704; 545258</t>
+          <t>273946; 302134</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>537411; 569981</t>
+          <t>537939; 570571</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>609912; 636922</t>
+          <t>612891; 637286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>624066; 657327</t>
+          <t>623606; 657134</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>579561; 815314</t>
+          <t>483420; 530906</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203749</t>
+          <t>222178</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>325379</t>
+          <t>353012</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>529127</t>
+          <t>575190</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>186186; 201800</t>
+          <t>185940; 201391</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228793; 243440</t>
+          <t>230019; 243683</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>232261; 246847</t>
+          <t>232867; 246517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>191394; 214947</t>
+          <t>208718; 235853</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>310479; 326332</t>
+          <t>310298; 326006</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>370611; 384354</t>
+          <t>369698; 383545</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>377794; 393809</t>
+          <t>375921; 393709</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>312495; 337242</t>
+          <t>340023; 366548</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>501991; 524118</t>
+          <t>502494; 524339</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>604784; 624461</t>
+          <t>604674; 624830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>615331; 637126</t>
+          <t>615843; 637071</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>511715; 545290</t>
+          <t>557610; 594579</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1318774</t>
+          <t>1397982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1778817</t>
+          <t>1728788</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3097592</t>
+          <t>3126771</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1520616; 1636835</t>
+          <t>1523547; 1639290</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1850019; 1965044</t>
+          <t>1844031; 1970458</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1714718; 1829476</t>
+          <t>1708608; 1830690</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1022275; 1443659</t>
+          <t>1339425; 1464117</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2105314; 2214989</t>
+          <t>2098769; 2211245</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2409124; 2519358</t>
+          <t>2401120; 2517117</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2204921; 2318325</t>
+          <t>2200429; 2313834</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1633608; 2158123</t>
+          <t>1679038; 1785648</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655098; 3821684</t>
+          <t>3649928; 3815091</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4292739; 4457638</t>
+          <t>4284597; 4451431</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3954961; 4114052</t>
+          <t>3947609; 4111313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2822782; 3424282</t>
+          <t>3042214; 3215997</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
